--- a/daily_matches/job_matches_2026-06-04.xlsx
+++ b/daily_matches/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Junior Full Stack Developer (Python/React.js)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526f04da000b8153</t>
+          <t>https://www.indeed.com/viewjob?jk=1c5b319fe293dd37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Full Stack Developer (Python/React.js)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f18524a0d1c2e02e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bc5f2994a1da28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, FastAPI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
+          <t>https://www.indeed.com/viewjob?jk=936e44ddac734d7b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Harvard Services Group, Inc</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, LLaMA, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Snowflake, Redshift, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b9d95984b1f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=98137df2f9a11a45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Senior Machine Learning Engineer, Model Risk Management</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harvard Maintenance, Inc.</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, LLaMA, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake</t>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, XGBoost, LightGBM, GCP Vertex AI, MLflow, Git, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780346cd358075a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Gluware, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Glue, BigQuery, CI/CD, Terraform, Snowflake, BigQuery</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
+          <t>https://www.indeed.com/viewjob?jk=998410ee3c90d993</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Glue, Redshift, Kinesis, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Snowflake, BigQuery, Redshift, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e808d31f6fa032cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfde2e65a7bc1cc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, Redshift, MLflow, Docker, Kubernetes, Jenkins, Terraform, Snowflake</t>
+          <t>Data Scientist, XGBoost, Docker, PySpark, Kafka, Hadoop, NoSQL, Tableau, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58a2b9f1b9c3a51</t>
+          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, PostgreSQL, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4544c5c153a39f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f048af853f53c2d2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CarParts.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e58bc4277f70431</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea29a3880a03255</t>
+          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>AI LLM Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3cb19cae9db9b</t>
+          <t>https://www.indeed.com/viewjob?jk=77cc10c4736bb6e5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Information Technology - BI Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, CI/CD</t>
+          <t>Data Scientist, RAG, Data Lake, Dataflow, CI/CD, Git, Databricks, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098cb973641601aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7533e66ad7d7d8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL</t>
+          <t>Data Scientist, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, spaCy, FastAPI, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6489a28686bb801b</t>
+          <t>https://www.indeed.com/viewjob?jk=4379bc5dbb18bfc7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MongoDB, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86eb595a514ce2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=cacc6222d3252e09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Agentforce Forward Deployed Engineer B2C Commerce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f26d4983647c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f016a5fc5c9606fb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Java Engineer (OpenText Exstream) (FTE/Onsite/Hybrid)</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1116aa11ed979d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b90bf1b03ba9d70</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer - Python - Loops</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Copperleaf Technologies Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf2b7b77b7ef545</t>
+          <t>https://www.indeed.com/viewjob?jk=44d54523041a6593</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer - Innovation Lab</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, CI/CD, Git, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34e71088bb8e761</t>
+          <t>https://www.indeed.com/viewjob?jk=84483d87d901b74f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer Level 3 (FullStack)</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ohio City, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, CI/CD, Terraform, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010f30f9c6b2bb8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d38569492546a2a5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Java &amp; OpenText Extreme</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd6ce5169df5e00d</t>
+          <t>https://www.indeed.com/viewjob?jk=429d975959713c02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist I - Customer Lifecycle</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0aa8a8af53003cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3627aa815bcb26b1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software engineer, connectors &amp; MCP</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfcca28ee365483</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab8b05c5c83b546</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software engineer, connectors &amp; MCP</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc103894281c591</t>
+          <t>https://www.indeed.com/viewjob?jk=504fbb317a979661</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software engineer, connectors &amp; MCP</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fd2dbc7873fe32</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ee593cfe0c6e2a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, GenAI</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=920baef5f2aad813</t>
+          <t>https://www.indeed.com/viewjob?jk=67ff580d749766b3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Developer I - Data Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Git, Snowflake, Kafka, Polars, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ed8e8fc2e11cb20c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer - Orchestration Platform, Temporal, Fleet Management (Flexibility on level)</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7de82ebac5919bb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5ef194f6030b32</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - SAP Test Automation</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cddae0ef059e63d</t>
+          <t>https://www.indeed.com/viewjob?jk=50300313b05ef2fe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e8be79fa6bbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb63327fcfabb15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Automation Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Cortex, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb4fc7fa9b9442c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed00428633a0b1c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - USDS</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a12b09835e370c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ce50d183040d4e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Business Optimization &amp; ML Governance</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8957f79f7333b87</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6c76d3973fb9fe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Applied Intuition</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88d783311283a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=8653b1d4dd59a757</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b77bb7abd26633d</t>
+          <t>https://www.indeed.com/viewjob?jk=79bef04894e09345</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Founding Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, MySQL, NoSQL, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7306e710e33f7ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=bab75ff81b700427</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b1215a475fcdf9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0666607a4053af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (React/Typescript)</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vertafore</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757afec97d5d27e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6268b2c2e449dea</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b910ec252456f</t>
+          <t>https://www.indeed.com/viewjob?jk=871fd9a4c7882117</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f29fb8b41e231f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b61fa629e393ac4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bfd933004fe4db</t>
+          <t>https://www.indeed.com/viewjob?jk=a60734d2d444c25d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ombud</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1923b9abc650d810</t>
+          <t>https://www.indeed.com/viewjob?jk=c8f9e107b12cf2c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Capgemini Invent - Contextual Systems Engineer Senior Consultant</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Git, Snowflake, BigQuery, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3629f89affa3c180</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b56a7b8e1920bb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78e27c5992617d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b8f5cbe028b8b5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Agentic AI Architect</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49092c9ac5159afc</t>
+          <t>https://www.indeed.com/viewjob?jk=af96f369db88fb99</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Infrastructure - USDS</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c5e20188614e05</t>
+          <t>https://www.indeed.com/viewjob?jk=fa15441f242c3734</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, AI Search - USDS</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b577906eefbf65c4</t>
+          <t>https://www.indeed.com/viewjob?jk=56e464f47370f1c6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Infrastructure - USDS</t>
+          <t>Agentic Delivery Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3aa9de9d956cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=eccc34aa4b9e3a67</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Probably Genetic</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Prompt Engineering, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ac55ea6006e7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=77981b463142c769</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Software Engineer (Project Hire)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Summit School Services LLC.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Warrenville, IL, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Hypothesis Testing, A/B Testing</t>
+          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9416a7882ebdf86</t>
+          <t>https://www.indeed.com/viewjob?jk=8384ffc5095926d3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist - Tech focus - Top Secret required to apply - DC area</t>
+          <t>Software Engineer - AI &amp; Edge Kubernetes Orchestration - San Jose, CA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>ZEDEDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Data Scientist, OpenCV, Hadoop, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, Copilot, TensorFlow, PyTorch, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a680d47fe21434d</t>
+          <t>https://www.indeed.com/viewjob?jk=619a172bed667e85</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WPP</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6011a73d7f9fa67</t>
+          <t>https://www.indeed.com/viewjob?jk=c750f99460ec29c8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fd9da578afe01bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1362fcbb2b1a08</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Machine Learning Engineer - Generative AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ff4aea4df636b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c66f46ae2450f0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, PyTorch, GCP Vertex AI, Azure ML, Databricks, R</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e6a1216511bc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c41d1d5393c15e39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Learning Perception Engineer - SLAM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Python, R, Scala, Optimization</t>
+          <t>RAG, Synapse, Dataflow, CI/CD, Git, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,137 +2421,137 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ee0150407e850e</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe727a6834d5b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning Infrastructure - USDS</t>
+          <t>Internship, Software Machine Learning Engineer, Reliability Energy Engineering (Fall 2026)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, Kubernetes, Hadoop, Python, R</t>
+          <t>Machine Learning Engineer, RAG, FastAPI, CI/CD, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fac03aad77528fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f6eeb09dbfa43c0e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
+          <t>FULL STACK PYTHON DEVELOPER — AI &amp; CRYPTO MARKET ANALYSIS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>smb enterprises</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, Kafka, MySQL, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Docker, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
+          <t>https://www.indeed.com/viewjob?jk=eca2821bd503cad2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Emerging Product - USDS</t>
+          <t>Machine Learning Engineer III, Core Agents</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Kubernetes, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1690a344af471ac3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e82f00a99420271</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Machine Learning Infrastructure - USDS</t>
+          <t>Senior Backend Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Conversica</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, Kubernetes, Hadoop, Python, R</t>
+          <t>AI Engineer, RAG, Redshift, FastAPI, Terraform, Git, Redshift, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9726fe96b78c049b</t>
+          <t>https://www.indeed.com/viewjob?jk=33a4cf2c627cc8ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,42 +2596,287 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1362d2ec38f292</t>
+          <t>https://www.indeed.com/viewjob?jk=1574989b13cbf030</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Consultant - Analytics</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Kubernetes, Jenkins, Git, Kafka, Hadoop, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26d05b8ec42e7cf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Total Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2100298ef765370d</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Bambee</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>10</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27d85838748f307d</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e3ad167874c8532</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Engineer 5 - Contingent (contract)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Copilot, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecac5856d972d587</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HIROSE ELECTRIC USA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Downers Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d43930f3049c70f</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43e93c9e298a942b</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20e0b2d11759a5ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07a15a46927f13a9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-04.xlsx
+++ b/daily_matches/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, AWS SageMaker, S3, Glue, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,172 +496,172 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineering</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>Octus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Azure ML</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, S3, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73906a4c3d4b3903</t>
+          <t>https://www.indeed.com/viewjob?jk=04198c96d0c6e610</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Developer</t>
+          <t>Co-op: Engineering, Data Science (Fall 2026)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>Volvo Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Databricks, PostgreSQL, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Power BI, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
+          <t>https://www.indeed.com/viewjob?jk=c328bf0f2c61c7ec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Science &amp; Advanced Analytics</t>
+          <t>Sr Software Engineer (Project Hire)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604c36e27fd46c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=db389a6d7f181695</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>FSS Government Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e7f453e9103613</t>
+          <t>https://www.indeed.com/viewjob?jk=50d5698ac8d91221</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AdTech</t>
+          <t>Senior Data scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manchester, NH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, S3, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1a29e5f16bf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b9ab7d3e2dc8c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AdTech</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Roku</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, S3, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Data Lake, Git, Snowflake, Databricks, Kafka, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45844ce996d8382</t>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3D Computer Vision Engineer</t>
+          <t>Senior Consultant - Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FIT:MATCH.AI</t>
+          <t>Torq</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7ea143f1138c8c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e4a262cd4cf345</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist, D2C Data Science</t>
+          <t>Account Solution Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CoreWeave, Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e12fabb9f8b7685</t>
+          <t>https://www.indeed.com/viewjob?jk=be1d075f96cd8e5f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Customer Lifecycle Analyst</t>
+          <t>Account Solution Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>CoreWeave, Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5460eaebdcd217</t>
+          <t>https://www.indeed.com/viewjob?jk=afb6118ea67a2981</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Researcher III (Full Time) - United States</t>
+          <t>Senior Software Engineer - Java (AMS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd68274db90ff70a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6eccf51d149650a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. BI Commercial Data Analyst</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d2a11ea913dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=f23852102a30f410</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Threat Detection Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8328baadaf33690a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f23266b7751c67</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI &amp; ML Engineer</t>
+          <t>AI/ML Engineer(Entry Level)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Parahunt Global Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,87 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, AWS SageMaker, Snowflake, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55495213861de145</t>
+          <t>https://www.indeed.com/viewjob?jk=7128bda361b8a340</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BridgeNexus Technologies Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Austin, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72f35112462a49bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Decision Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CRNCY Group</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, Python, SQL, R, Scala, Optimization, Bayesian, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc303bf90aea1f0f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-04.xlsx
+++ b/daily_matches/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
+          <t>AI Applied Architect (.NET &amp; Databricks)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>Data Scientist, LangChain, RAG, FAISS, Pinecone, Azure ML, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Octus</t>
+          <t>BONbLOC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, S3, Docker, CI/CD, Git</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04198c96d0c6e610</t>
+          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Co-op: Engineering, Data Science (Fall 2026)</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Volvo Group</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Power BI, Matplotlib, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, BigQuery, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c328bf0f2c61c7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Project Hire)</t>
+          <t>Full Stack Engineer (Contract) - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Tech Holding</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db389a6d7f181695</t>
+          <t>https://www.indeed.com/viewjob?jk=86d30d5cb5661e65</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FSS Government Solutions</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, CI/CD, Terraform, Databricks, Dask, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d5698ac8d91221</t>
+          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data scientist</t>
+          <t>.Net Developer with AI Expertise (GitHub Copilot, Claude, AI/ML) | Remote | USC/GC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tms Llc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mount Juliet, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Azure ML, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b9ab7d3e2dc8c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e061486a8bbba5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Algorized</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Git, Snowflake, Databricks, Kafka, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Consultant - Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, S3, EC2, FastAPI, Docker, Kubernetes, Jenkins, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e4a262cd4cf345</t>
+          <t>https://www.indeed.com/viewjob?jk=ea95529566393148</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Account Solution Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CoreWeave, Inc</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1d075f96cd8e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=59096f4fac812823</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Account Solution Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CoreWeave, Inc</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb6118ea67a2981</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed71fc6692e6c45</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java (AMS)</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, Copilot, BigQuery, AKS, Snowflake, Databricks, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6eccf51d149650a</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - AI/ML Engineer - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Pinecone, TensorFlow, PyTorch, AKS, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23852102a30f410</t>
+          <t>https://www.indeed.com/viewjob?jk=2260707de1275f93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer - Growth</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f23266b7751c67</t>
+          <t>https://www.indeed.com/viewjob?jk=41858670434b034b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI/ML Engineer(Entry Level)</t>
+          <t>Engineer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Parahunt Global Solutions</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7128bda361b8a340</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Dye Capital &amp; Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, IN, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,742 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f35112462a49bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d82debab78624a75</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Decision Scientist</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CRNCY Group</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Databricks, Python, SQL, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f71576f5ead3408</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Databricks, Python, SQL, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6c680fe43376445</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Databricks, Python, SQL, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6874dcd44e91264</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DevIQ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Git, Databricks, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b33a2a90b6a40547</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Manufacturing Data Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ion Storage Systems</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Beltsville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Dataflow, Docker, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Infrastructure Support Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nSCALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98a95d1be0800a13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Infrastructure Support Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nSCALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2656268a51f1d02c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, FastAPI, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=933f0f930c6c81e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer - Remote US</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pulsora</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99af23f4da4e2de9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Test Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=511a4c42af4dcb3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3444cb97a837af</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, Python, SQL, R, Scala, Optimization, Bayesian, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc303bf90aea1f0f</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, CI/CD, Git, Databricks, Kafka, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7574fc6f75e3b61</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GCP Senior Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>West Monroe</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa2b5c5487f46437</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cotality</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=131cb753a101445c</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote - United States)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nextech Systems</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Databricks, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - API &amp; MCP Platform</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e8549433f1a2275</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - API &amp; MCP Platform</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6a1b8aa682e4f28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CLERA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>S3, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b36182e936292fa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f14677393b298393</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-04.xlsx
+++ b/daily_matches/job_matches_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Applied Architect (.NET &amp; Databricks)</t>
+          <t>Databricks Expert / Data Lakehouse Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Bilink Corp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, FAISS, Pinecone, Azure ML, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef7670a3dacf51f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BONbLOC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, BigQuery, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
+          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Contract) - Remote</t>
+          <t>Senior AI Cyber Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech Holding</t>
+          <t>ImmunityBio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Azure ML, Data Lake, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d30d5cb5661e65</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73a29a7c0a3158</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>LP Building Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, CI/CD, Terraform, Databricks, Dask, Python</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5f5a2365232f0c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>.Net Developer with AI Expertise (GitHub Copilot, Claude, AI/ML) | Remote | USC/GC</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Juliet, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Azure ML, CI/CD, Git, Python</t>
+          <t>AI Engineer, Data Scientist, RAG, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e061486a8bbba5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Algorized</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c88a8d02f220104</t>
+          <t>https://www.indeed.com/viewjob?jk=197d2ca1196855f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Docker, Kubernetes, Jenkins, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea95529566393148</t>
+          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Beacon Biosignals</t>
+          <t>eHub</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, S3, Glue, Redshift, CI/CD, Redshift, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59096f4fac812823</t>
+          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Corporate Planning &amp; Management, Data Engineering, New York, Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Beacon Biosignals</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, PySpark, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed71fc6692e6c45</t>
+          <t>https://www.indeed.com/viewjob?jk=c58cbc4b6d6a6ff5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Agentic AI and DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>A P Ventures LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, BigQuery, AKS, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ccdded8843392c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - AI/ML Engineer - Sr Associate/Consultant</t>
+          <t>Senior Software Engineer, AI Products</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Pinecone, TensorFlow, PyTorch, AKS, Python</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2260707de1275f93</t>
+          <t>https://www.indeed.com/viewjob?jk=da09e03b36e1e430</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Growth</t>
+          <t>Senior Software Engineer, Engineering Enablement</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41858670434b034b</t>
+          <t>https://www.indeed.com/viewjob?jk=1988ac68e805bf31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer III, Platform Engineering</t>
+          <t>Senior Data Pipeline &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>fullstory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
+          <t>https://www.indeed.com/viewjob?jk=3fdbc5ce002f18fa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Agentic AI and DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dye Capital &amp; Company</t>
+          <t>A P Ventures LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Git, MySQL, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82debab78624a75</t>
+          <t>https://www.indeed.com/viewjob?jk=60fbfd36e06e0dd4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI / Agent Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=4b689497dcce77cd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Barr Engineering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Databricks, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f71576f5ead3408</t>
+          <t>https://www.indeed.com/viewjob?jk=7a294861254df3eb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Infrastructure Automation &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Databricks, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>AI Engineer, Generative AI, RAG, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c680fe43376445</t>
+          <t>https://www.indeed.com/viewjob?jk=e7163efbdbe5c29e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Databricks, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>RAG, S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6874dcd44e91264</t>
+          <t>https://www.indeed.com/viewjob?jk=a178ad24359ae8e4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DevIQ</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Git, Databricks, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, PostgreSQL, Cassandra, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
+          <t>https://www.indeed.com/viewjob?jk=228794e7a023d66c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33a2a90b6a40547</t>
+          <t>https://www.indeed.com/viewjob?jk=a496c3d5484fc469</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manufacturing Data Systems Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Docker, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+          <t>https://www.indeed.com/viewjob?jk=74cb35fce77a6863</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Infrastructure Support Engineer</t>
+          <t>Frontend Engineer (Contract) - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Tech Holding</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Terraform, Git, Kafka, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a95d1be0800a13</t>
+          <t>https://www.indeed.com/viewjob?jk=f8a9c05aeca75e6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Infrastructure Support Engineer</t>
+          <t>Azure &amp; AI Modern Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Epicsoft Tech</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Terraform, Snowflake, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2656268a51f1d02c</t>
+          <t>https://www.indeed.com/viewjob?jk=5add5f22db9949d8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DevEx Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, FastAPI, Git, MySQL, Python, SQL, R</t>
+          <t>S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933f0f930c6c81e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e18ca46c38b8eca9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Remote US</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pulsora</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, MLflow, Databricks, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,357 +1371,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99af23f4da4e2de9</t>
+          <t>https://www.indeed.com/viewjob?jk=e2a3fe5560e6bcb6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Data Scientist / Data Science Consultant – 1898 &amp; Co.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Burns &amp; McDonnell</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a4c42af4dcb3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db3444cb97a837af</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CoStar Group</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Kinesis, CI/CD, Git, Databricks, Kafka, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7574fc6f75e3b61</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>GCP Senior Architect</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>West Monroe</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2b5c5487f46437</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Cotality</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=131cb753a101445c</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Engineer (Remote - United States)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nextech Systems</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Databricks, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - API &amp; MCP Platform</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ZoomInfo</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8549433f1a2275</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - API &amp; MCP Platform</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ZoomInfo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a1b8aa682e4f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CLERA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>S3, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b36182e936292fa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sr. Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>PlayStation</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f14677393b298393</t>
+          <t>https://www.indeed.com/viewjob?jk=5949a1364d38c5d1</t>
         </is>
       </c>
     </row>
